--- a/tai_chinh_test.xlsx
+++ b/tai_chinh_test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thein\Desktop\demo_cnpm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Study\NMCNPM\Code\branch2\Mall_Management_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6849A28B-A994-4440-B15F-4AD27273B776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF5059-1322-42D5-933F-D7B3B660E2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5856" yWindow="2172" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>GHICHU</t>
   </si>
   <si>
-    <t>HD_TEST_001</t>
-  </si>
-  <si>
     <t>Tiền thuê</t>
   </si>
   <si>
@@ -76,16 +73,25 @@
   </si>
   <si>
     <t>Giảm trừ</t>
+  </si>
+  <si>
+    <t>HD_SEED_001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -401,6 +407,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -422,9 +434,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1">
         <v>5</v>
@@ -433,18 +445,18 @@
         <v>2026</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1">
         <v>15000000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
@@ -453,18 +465,18 @@
         <v>2026</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1">
         <v>1200000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1">
         <v>5</v>
@@ -473,18 +485,18 @@
         <v>2026</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
         <v>300000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>5</v>
@@ -493,18 +505,18 @@
         <v>2026</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1">
         <v>500000</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -513,16 +525,17 @@
         <v>2026</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>200000</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>